--- a/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/20gps/3mps_analysis.xlsx
+++ b/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/20gps/3mps_analysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Time</t>
   </si>
@@ -79,13 +79,34 @@
     <t>Q</t>
   </si>
   <si>
-    <t>rolling_std</t>
-  </si>
-  <si>
     <t>steady_state</t>
   </si>
   <si>
-    <t>avg_Q_steady</t>
+    <t>Averages</t>
+  </si>
+  <si>
+    <t>RTD_OUT_unc</t>
+  </si>
+  <si>
+    <t>RTD_IN_unc</t>
+  </si>
+  <si>
+    <t>RTD_unc</t>
+  </si>
+  <si>
+    <t>Delta_RTD</t>
+  </si>
+  <si>
+    <t>Rel_unc</t>
+  </si>
+  <si>
+    <t>ABS_unc</t>
+  </si>
+  <si>
+    <t>Average Q (W)</t>
+  </si>
+  <si>
+    <t>Average Q Uncertainty (W)</t>
   </si>
 </sst>
 </file>
@@ -421,10 +442,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X36"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -497,8 +518,23 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:29">
       <c r="A2" s="1">
         <v>46068.60502706018</v>
       </c>
@@ -562,14 +598,32 @@
       <c r="U2">
         <v>534.69073375145</v>
       </c>
-      <c r="W2" t="b">
-        <v>0</v>
+      <c r="V2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W2" t="s">
+        <v>29</v>
       </c>
       <c r="X2">
-        <v>530.4446240851555</v>
+        <v>0.250204254</v>
+      </c>
+      <c r="Y2">
+        <v>0.262245484</v>
+      </c>
+      <c r="Z2">
+        <v>0.3624567044463253</v>
+      </c>
+      <c r="AA2">
+        <v>6.020614999999999</v>
+      </c>
+      <c r="AB2">
+        <v>0.06102748236388002</v>
+      </c>
+      <c r="AC2">
+        <v>32.63082932414669</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:29">
       <c r="A3" s="1">
         <v>46068.60514280092</v>
       </c>
@@ -633,11 +687,32 @@
       <c r="U3">
         <v>536.9385848392252</v>
       </c>
-      <c r="W3" t="b">
-        <v>0</v>
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3">
+        <v>531.6681670040086</v>
+      </c>
+      <c r="X3">
+        <v>0.250218236</v>
+      </c>
+      <c r="Y3">
+        <v>0.262268722</v>
+      </c>
+      <c r="Z3">
+        <v>0.3624831694940677</v>
+      </c>
+      <c r="AA3">
+        <v>6.025242999999996</v>
+      </c>
+      <c r="AB3">
+        <v>0.0609861990390838</v>
+      </c>
+      <c r="AC3">
+        <v>32.74584340676897</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:29">
       <c r="A4" s="1">
         <v>46068.60525912037</v>
       </c>
@@ -701,14 +776,32 @@
       <c r="U4">
         <v>534.7738917792663</v>
       </c>
-      <c r="V4">
-        <v>1.274470204584158</v>
-      </c>
-      <c r="W4" t="b">
+      <c r="V4" t="b">
         <v>1</v>
       </c>
+      <c r="W4" t="s">
+        <v>30</v>
+      </c>
+      <c r="X4">
+        <v>0.25023603</v>
+      </c>
+      <c r="Y4">
+        <v>0.262283048</v>
+      </c>
+      <c r="Z4">
+        <v>0.3625058178544604</v>
+      </c>
+      <c r="AA4">
+        <v>6.023508999999997</v>
+      </c>
+      <c r="AB4">
+        <v>0.06100699243527931</v>
+      </c>
+      <c r="AC4">
+        <v>32.62494677036257</v>
+      </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:29">
       <c r="A5" s="1">
         <v>46068.60537486111</v>
       </c>
@@ -772,14 +865,32 @@
       <c r="U5">
         <v>532.0020112348622</v>
       </c>
-      <c r="V5">
-        <v>2.474502534098995</v>
-      </c>
-      <c r="W5" t="b">
+      <c r="V5" t="b">
         <v>1</v>
       </c>
+      <c r="W5">
+        <v>32.59461441848617</v>
+      </c>
+      <c r="X5">
+        <v>0.250249376</v>
+      </c>
+      <c r="Y5">
+        <v>0.262284958</v>
+      </c>
+      <c r="Z5">
+        <v>0.3625164125683845</v>
+      </c>
+      <c r="AA5">
+        <v>6.017791000000003</v>
+      </c>
+      <c r="AB5">
+        <v>0.06106514023404468</v>
+      </c>
+      <c r="AC5">
+        <v>32.48677742085067</v>
+      </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:29">
       <c r="A6" s="1">
         <v>46068.60549060185</v>
       </c>
@@ -843,14 +954,29 @@
       <c r="U6">
         <v>536.0459666273142</v>
       </c>
-      <c r="V6">
-        <v>2.06781170111564</v>
-      </c>
-      <c r="W6" t="b">
+      <c r="V6" t="b">
         <v>1</v>
       </c>
+      <c r="X6">
+        <v>0.250259544</v>
+      </c>
+      <c r="Y6">
+        <v>0.262281138</v>
+      </c>
+      <c r="Z6">
+        <v>0.3625206679813759</v>
+      </c>
+      <c r="AA6">
+        <v>6.010796999999997</v>
+      </c>
+      <c r="AB6">
+        <v>0.06113498801340927</v>
+      </c>
+      <c r="AC6">
+        <v>32.77116374439724</v>
+      </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:29">
       <c r="A7" s="1">
         <v>46068.60560692129</v>
       </c>
@@ -914,14 +1040,29 @@
       <c r="U7">
         <v>535.1902461805591</v>
       </c>
-      <c r="V7">
-        <v>2.13114502744811</v>
-      </c>
-      <c r="W7" t="b">
+      <c r="V7" t="b">
         <v>1</v>
       </c>
+      <c r="X7">
+        <v>0.250257002</v>
+      </c>
+      <c r="Y7">
+        <v>0.262286868</v>
+      </c>
+      <c r="Z7">
+        <v>0.3625230588187149</v>
+      </c>
+      <c r="AA7">
+        <v>6.014932999999999</v>
+      </c>
+      <c r="AB7">
+        <v>0.06109446751288908</v>
+      </c>
+      <c r="AC7">
+        <v>32.69716310849328</v>
+      </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:29">
       <c r="A8" s="1">
         <v>46068.60572266204</v>
       </c>
@@ -985,14 +1126,29 @@
       <c r="U8">
         <v>531.8903799682477</v>
       </c>
-      <c r="V8">
-        <v>2.194321268758766</v>
-      </c>
-      <c r="W8" t="b">
+      <c r="V8" t="b">
         <v>1</v>
       </c>
+      <c r="X8">
+        <v>0.250255096</v>
+      </c>
+      <c r="Y8">
+        <v>0.262287504</v>
+      </c>
+      <c r="Z8">
+        <v>0.3625222032214293</v>
+      </c>
+      <c r="AA8">
+        <v>6.016204000000002</v>
+      </c>
+      <c r="AB8">
+        <v>0.0610817660614679</v>
+      </c>
+      <c r="AC8">
+        <v>32.48880375956578</v>
+      </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:29">
       <c r="A9" s="1">
         <v>46068.60583840278</v>
       </c>
@@ -1056,14 +1212,29 @@
       <c r="U9">
         <v>532.0888055066545</v>
       </c>
-      <c r="V9">
-        <v>1.850559553540304</v>
-      </c>
-      <c r="W9" t="b">
+      <c r="V9" t="b">
         <v>1</v>
       </c>
+      <c r="X9">
+        <v>0.250265582</v>
+      </c>
+      <c r="Y9">
+        <v>0.262295144</v>
+      </c>
+      <c r="Z9">
+        <v>0.3625349694853994</v>
+      </c>
+      <c r="AA9">
+        <v>6.014780999999999</v>
+      </c>
+      <c r="AB9">
+        <v>0.06109792360076031</v>
+      </c>
+      <c r="AC9">
+        <v>32.50952118766538</v>
+      </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:29">
       <c r="A10" s="1">
         <v>46068.60595414352</v>
       </c>
@@ -1127,14 +1298,29 @@
       <c r="U10">
         <v>533.1576939090739</v>
       </c>
-      <c r="V10">
-        <v>0.6816621518671241</v>
-      </c>
-      <c r="W10" t="b">
+      <c r="V10" t="b">
         <v>1</v>
       </c>
+      <c r="X10">
+        <v>0.250275432</v>
+      </c>
+      <c r="Y10">
+        <v>0.262303738</v>
+      </c>
+      <c r="Z10">
+        <v>0.3625479869362941</v>
+      </c>
+      <c r="AA10">
+        <v>6.014153</v>
+      </c>
+      <c r="AB10">
+        <v>0.06110626785821162</v>
+      </c>
+      <c r="AC10">
+        <v>32.57927685467428</v>
+      </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:29">
       <c r="A11" s="1">
         <v>46068.60607046296</v>
       </c>
@@ -1198,14 +1384,29 @@
       <c r="U11">
         <v>531.392208940269</v>
       </c>
-      <c r="V11">
-        <v>0.8892605887477352</v>
-      </c>
-      <c r="W11" t="b">
+      <c r="V11" t="b">
         <v>1</v>
       </c>
+      <c r="X11">
+        <v>0.250293226</v>
+      </c>
+      <c r="Y11">
+        <v>0.26231106</v>
+      </c>
+      <c r="Z11">
+        <v>0.3625655681112186</v>
+      </c>
+      <c r="AA11">
+        <v>6.008916999999997</v>
+      </c>
+      <c r="AB11">
+        <v>0.06116097521074883</v>
+      </c>
+      <c r="AC11">
+        <v>32.50046571818086</v>
+      </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:29">
       <c r="A12" s="1">
         <v>46068.60618678241</v>
       </c>
@@ -1269,14 +1470,29 @@
       <c r="U12">
         <v>532.4079405603691</v>
       </c>
-      <c r="V12">
-        <v>0.8860754278500933</v>
-      </c>
-      <c r="W12" t="b">
+      <c r="V12" t="b">
         <v>1</v>
       </c>
+      <c r="X12">
+        <v>0.250309432</v>
+      </c>
+      <c r="Y12">
+        <v>0.262323158</v>
+      </c>
+      <c r="Z12">
+        <v>0.3625855084959348</v>
+      </c>
+      <c r="AA12">
+        <v>6.006863000000003</v>
+      </c>
+      <c r="AB12">
+        <v>0.06118460469741174</v>
+      </c>
+      <c r="AC12">
+        <v>32.57516938094927</v>
+      </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:29">
       <c r="A13" s="1">
         <v>46068.60630310185</v>
       </c>
@@ -1340,14 +1556,29 @@
       <c r="U13">
         <v>530.8950416215633</v>
       </c>
-      <c r="V13">
-        <v>0.7711192369856048</v>
-      </c>
-      <c r="W13" t="b">
+      <c r="V13" t="b">
         <v>1</v>
       </c>
+      <c r="X13">
+        <v>0.250314516</v>
+      </c>
+      <c r="Y13">
+        <v>0.262323158</v>
+      </c>
+      <c r="Z13">
+        <v>0.362589018233326</v>
+      </c>
+      <c r="AA13">
+        <v>6.004321000000004</v>
+      </c>
+      <c r="AB13">
+        <v>0.06121039280292227</v>
+      </c>
+      <c r="AC13">
+        <v>32.49629403477966</v>
+      </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:29">
       <c r="A14" s="1">
         <v>46068.6064188426</v>
       </c>
@@ -1411,14 +1642,29 @@
       <c r="U14">
         <v>530.7615615988263</v>
       </c>
-      <c r="V14">
-        <v>0.914443710725791</v>
-      </c>
-      <c r="W14" t="b">
+      <c r="V14" t="b">
         <v>1</v>
       </c>
+      <c r="X14">
+        <v>0.250323414</v>
+      </c>
+      <c r="Y14">
+        <v>0.262321884</v>
+      </c>
+      <c r="Z14">
+        <v>0.3625942393667126</v>
+      </c>
+      <c r="AA14">
+        <v>5.999234999999999</v>
+      </c>
+      <c r="AB14">
+        <v>0.06126175960884384</v>
+      </c>
+      <c r="AC14">
+        <v>32.51538719628186</v>
+      </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:29">
       <c r="A15" s="1">
         <v>46068.60653458333</v>
       </c>
@@ -1482,14 +1728,29 @@
       <c r="U15">
         <v>530.4733791622338</v>
       </c>
-      <c r="V15">
-        <v>0.2155091888348731</v>
-      </c>
-      <c r="W15" t="b">
+      <c r="V15" t="b">
         <v>1</v>
       </c>
+      <c r="X15">
+        <v>0.250315152</v>
+      </c>
+      <c r="Y15">
+        <v>0.262318064</v>
+      </c>
+      <c r="Z15">
+        <v>0.3625857719512601</v>
+      </c>
+      <c r="AA15">
+        <v>6.001456000000005</v>
+      </c>
+      <c r="AB15">
+        <v>0.06123830029351058</v>
+      </c>
+      <c r="AC15">
+        <v>32.48528809085017</v>
+      </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:29">
       <c r="A16" s="1">
         <v>46068.60665032407</v>
       </c>
@@ -1553,14 +1814,29 @@
       <c r="U16">
         <v>534.2811882811953</v>
       </c>
-      <c r="V16">
-        <v>2.12015059946408</v>
-      </c>
-      <c r="W16" t="b">
+      <c r="V16" t="b">
         <v>1</v>
       </c>
+      <c r="X16">
+        <v>0.250313882</v>
+      </c>
+      <c r="Y16">
+        <v>0.262311378</v>
+      </c>
+      <c r="Z16">
+        <v>0.3625800581253315</v>
+      </c>
+      <c r="AA16">
+        <v>5.998747999999999</v>
+      </c>
+      <c r="AB16">
+        <v>0.06126426821598467</v>
+      </c>
+      <c r="AC16">
+        <v>32.73234602161416</v>
+      </c>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:29">
       <c r="A17" s="1">
         <v>46068.60676664352</v>
       </c>
@@ -1624,14 +1900,29 @@
       <c r="U17">
         <v>532.6526796535538</v>
       </c>
-      <c r="V17">
-        <v>1.910532267380575</v>
-      </c>
-      <c r="W17" t="b">
+      <c r="V17" t="b">
         <v>1</v>
       </c>
+      <c r="X17">
+        <v>0.25030689</v>
+      </c>
+      <c r="Y17">
+        <v>0.262316472</v>
+      </c>
+      <c r="Z17">
+        <v>0.3625789164637112</v>
+      </c>
+      <c r="AA17">
+        <v>6.004791000000004</v>
+      </c>
+      <c r="AB17">
+        <v>0.06120407001220129</v>
+      </c>
+      <c r="AC17">
+        <v>32.60051189770273</v>
+      </c>
     </row>
-    <row r="18" spans="1:23">
+    <row r="18" spans="1:29">
       <c r="A18" s="1">
         <v>46068.60688296297</v>
       </c>
@@ -1695,14 +1986,29 @@
       <c r="U18">
         <v>530.740297992841</v>
       </c>
-      <c r="V18">
-        <v>1.772340636968174</v>
-      </c>
-      <c r="W18" t="b">
+      <c r="V18" t="b">
         <v>1</v>
       </c>
+      <c r="X18">
+        <v>0.250320554</v>
+      </c>
+      <c r="Y18">
+        <v>0.26232443</v>
+      </c>
+      <c r="Z18">
+        <v>0.3625941068601251</v>
+      </c>
+      <c r="AA18">
+        <v>6.001938000000003</v>
+      </c>
+      <c r="AB18">
+        <v>0.06123488360939308</v>
+      </c>
+      <c r="AC18">
+        <v>32.49982037440622</v>
+      </c>
     </row>
-    <row r="19" spans="1:23">
+    <row r="19" spans="1:29">
       <c r="A19" s="1">
         <v>46068.60699928241</v>
       </c>
@@ -1766,14 +2072,29 @@
       <c r="U19">
         <v>533.3660452100897</v>
       </c>
-      <c r="V19">
-        <v>1.357733557708606</v>
-      </c>
-      <c r="W19" t="b">
+      <c r="V19" t="b">
         <v>1</v>
       </c>
+      <c r="X19">
+        <v>0.25032405</v>
+      </c>
+      <c r="Y19">
+        <v>0.262321566</v>
+      </c>
+      <c r="Z19">
+        <v>0.3625944483815146</v>
+      </c>
+      <c r="AA19">
+        <v>5.998758000000002</v>
+      </c>
+      <c r="AB19">
+        <v>0.06126653550999698</v>
+      </c>
+      <c r="AC19">
+        <v>32.67748974869062</v>
+      </c>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:29">
       <c r="A20" s="1">
         <v>46068.60711560185</v>
       </c>
@@ -1837,14 +2158,29 @@
       <c r="U20">
         <v>533.4423685222306</v>
       </c>
-      <c r="V20">
-        <v>1.538481873073682</v>
-      </c>
-      <c r="W20" t="b">
+      <c r="V20" t="b">
         <v>1</v>
       </c>
+      <c r="X20">
+        <v>0.250338348</v>
+      </c>
+      <c r="Y20">
+        <v>0.262328568</v>
+      </c>
+      <c r="Z20">
+        <v>0.3626093849699698</v>
+      </c>
+      <c r="AA20">
+        <v>5.995110000000004</v>
+      </c>
+      <c r="AB20">
+        <v>0.0613052811378335</v>
+      </c>
+      <c r="AC20">
+        <v>32.70283437308713</v>
+      </c>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:29">
       <c r="A21" s="1">
         <v>46068.6072319213</v>
       </c>
@@ -1908,14 +2244,29 @@
       <c r="U21">
         <v>531.3671376917835</v>
       </c>
-      <c r="V21">
-        <v>1.176721399649019</v>
-      </c>
-      <c r="W21" t="b">
+      <c r="V21" t="b">
         <v>1</v>
       </c>
+      <c r="X21">
+        <v>0.250332312</v>
+      </c>
+      <c r="Y21">
+        <v>0.262327932</v>
+      </c>
+      <c r="Z21">
+        <v>0.3626047577441062</v>
+      </c>
+      <c r="AA21">
+        <v>5.997810000000001</v>
+      </c>
+      <c r="AB21">
+        <v>0.06127765700480514</v>
+      </c>
+      <c r="AC21">
+        <v>32.56093320710217</v>
+      </c>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:29">
       <c r="A22" s="1">
         <v>46068.60734824074</v>
       </c>
@@ -1979,14 +2330,29 @@
       <c r="U22">
         <v>533.3255694450685</v>
       </c>
-      <c r="V22">
-        <v>1.165881637526957</v>
-      </c>
-      <c r="W22" t="b">
+      <c r="V22" t="b">
         <v>1</v>
       </c>
+      <c r="X22">
+        <v>0.250334536</v>
+      </c>
+      <c r="Y22">
+        <v>0.262330478</v>
+      </c>
+      <c r="Z22">
+        <v>0.3626081350466971</v>
+      </c>
+      <c r="AA22">
+        <v>5.997971</v>
+      </c>
+      <c r="AB22">
+        <v>0.06127661149541371</v>
+      </c>
+      <c r="AC22">
+        <v>32.68038371945575</v>
+      </c>
     </row>
-    <row r="23" spans="1:23">
+    <row r="23" spans="1:29">
       <c r="A23" s="1">
         <v>46068.60746456018</v>
       </c>
@@ -2050,14 +2416,29 @@
       <c r="U23">
         <v>532.2790698715306</v>
       </c>
-      <c r="V23">
-        <v>0.9799861045055623</v>
-      </c>
-      <c r="W23" t="b">
+      <c r="V23" t="b">
         <v>1</v>
       </c>
+      <c r="X23">
+        <v>0.250332312</v>
+      </c>
+      <c r="Y23">
+        <v>0.26232825</v>
+      </c>
+      <c r="Z23">
+        <v>0.3626049878026057</v>
+      </c>
+      <c r="AA23">
+        <v>5.997968999999998</v>
+      </c>
+      <c r="AB23">
+        <v>0.06127611369986712</v>
+      </c>
+      <c r="AC23">
+        <v>32.61599280550742</v>
+      </c>
     </row>
-    <row r="24" spans="1:23">
+    <row r="24" spans="1:29">
       <c r="A24" s="1">
         <v>46068.60758030092</v>
       </c>
@@ -2121,14 +2502,29 @@
       <c r="U24">
         <v>529.6428081376249</v>
       </c>
-      <c r="V24">
-        <v>1.89770774596917</v>
-      </c>
-      <c r="W24" t="b">
+      <c r="V24" t="b">
         <v>1</v>
       </c>
+      <c r="X24">
+        <v>0.250348516</v>
+      </c>
+      <c r="Y24">
+        <v>0.262326658</v>
+      </c>
+      <c r="Z24">
+        <v>0.3626150230766111</v>
+      </c>
+      <c r="AA24">
+        <v>5.989070999999996</v>
+      </c>
+      <c r="AB24">
+        <v>0.06136638234440697</v>
+      </c>
+      <c r="AC24">
+        <v>32.50226307013887</v>
+      </c>
     </row>
-    <row r="25" spans="1:23">
+    <row r="25" spans="1:29">
       <c r="A25" s="1">
         <v>46068.60769604167</v>
       </c>
@@ -2192,14 +2588,29 @@
       <c r="U25">
         <v>530.1176431339507</v>
       </c>
-      <c r="V25">
-        <v>1.405175537391945</v>
-      </c>
-      <c r="W25" t="b">
+      <c r="V25" t="b">
         <v>1</v>
       </c>
+      <c r="X25">
+        <v>0.250378386</v>
+      </c>
+      <c r="Y25">
+        <v>0.262325066</v>
+      </c>
+      <c r="Z25">
+        <v>0.3626344942609147</v>
+      </c>
+      <c r="AA25">
+        <v>5.97334</v>
+      </c>
+      <c r="AB25">
+        <v>0.06152692318939844</v>
+      </c>
+      <c r="AC25">
+        <v>32.61650751044751</v>
+      </c>
     </row>
-    <row r="26" spans="1:23">
+    <row r="26" spans="1:29">
       <c r="A26" s="1">
         <v>46068.60781236111</v>
       </c>
@@ -2263,14 +2674,29 @@
       <c r="U26">
         <v>529.8257109534989</v>
       </c>
-      <c r="V26">
-        <v>0.2394946456473387</v>
-      </c>
-      <c r="W26" t="b">
+      <c r="V26" t="b">
         <v>1</v>
       </c>
+      <c r="X26">
+        <v>0.250372666</v>
+      </c>
+      <c r="Y26">
+        <v>0.262329842</v>
+      </c>
+      <c r="Z26">
+        <v>0.3626339999003024</v>
+      </c>
+      <c r="AA26">
+        <v>5.978588000000002</v>
+      </c>
+      <c r="AB26">
+        <v>0.06147426061727016</v>
+      </c>
+      <c r="AC26">
+        <v>32.57064383688584</v>
+      </c>
     </row>
-    <row r="27" spans="1:23">
+    <row r="27" spans="1:29">
       <c r="A27" s="1">
         <v>46068.60792810185</v>
       </c>
@@ -2334,14 +2760,29 @@
       <c r="U27">
         <v>529.4078896733982</v>
       </c>
-      <c r="V27">
-        <v>0.3567326250949764</v>
-      </c>
-      <c r="W27" t="b">
+      <c r="V27" t="b">
         <v>1</v>
       </c>
+      <c r="X27">
+        <v>0.250375526</v>
+      </c>
+      <c r="Y27">
+        <v>0.262333344</v>
+      </c>
+      <c r="Z27">
+        <v>0.3626385078752655</v>
+      </c>
+      <c r="AA27">
+        <v>5.978909000000002</v>
+      </c>
+      <c r="AB27">
+        <v>0.06147179141620222</v>
+      </c>
+      <c r="AC27">
+        <v>32.54365136809493</v>
+      </c>
     </row>
-    <row r="28" spans="1:23">
+    <row r="28" spans="1:29">
       <c r="A28" s="1">
         <v>46068.60804384259</v>
       </c>
@@ -2405,14 +2846,29 @@
       <c r="U28">
         <v>530.572203197627</v>
       </c>
-      <c r="V28">
-        <v>0.5898377284388555</v>
-      </c>
-      <c r="W28" t="b">
+      <c r="V28" t="b">
         <v>1</v>
       </c>
+      <c r="X28">
+        <v>0.25039078</v>
+      </c>
+      <c r="Y28">
+        <v>0.262340346</v>
+      </c>
+      <c r="Z28">
+        <v>0.3626541049656106</v>
+      </c>
+      <c r="AA28">
+        <v>5.974782999999995</v>
+      </c>
+      <c r="AB28">
+        <v>0.06151569467819545</v>
+      </c>
+      <c r="AC28">
+        <v>32.6385176566427</v>
+      </c>
     </row>
-    <row r="29" spans="1:23">
+    <row r="29" spans="1:29">
       <c r="A29" s="1">
         <v>46068.60815958333</v>
       </c>
@@ -2476,14 +2932,29 @@
       <c r="U29">
         <v>531.0331403476114</v>
       </c>
-      <c r="V29">
-        <v>0.8376085793255422</v>
-      </c>
-      <c r="W29" t="b">
+      <c r="V29" t="b">
         <v>1</v>
       </c>
+      <c r="X29">
+        <v>0.250404762</v>
+      </c>
+      <c r="Y29">
+        <v>0.26233589</v>
+      </c>
+      <c r="Z29">
+        <v>0.3626605355071996</v>
+      </c>
+      <c r="AA29">
+        <v>5.965564000000001</v>
+      </c>
+      <c r="AB29">
+        <v>0.06160931253114467</v>
+      </c>
+      <c r="AC29">
+        <v>32.7165867080712</v>
+      </c>
     </row>
-    <row r="30" spans="1:23">
+    <row r="30" spans="1:29">
       <c r="A30" s="1">
         <v>46068.60827590278</v>
       </c>
@@ -2547,14 +3018,29 @@
       <c r="U30">
         <v>529.9402036917452</v>
       </c>
-      <c r="V30">
-        <v>0.5486949616131226</v>
-      </c>
-      <c r="W30" t="b">
+      <c r="V30" t="b">
         <v>1</v>
       </c>
+      <c r="X30">
+        <v>0.250391098</v>
+      </c>
+      <c r="Y30">
+        <v>0.262329206</v>
+      </c>
+      <c r="Z30">
+        <v>0.3626462660475577</v>
+      </c>
+      <c r="AA30">
+        <v>5.969054</v>
+      </c>
+      <c r="AB30">
+        <v>0.06157188111041396</v>
+      </c>
+      <c r="AC30">
+        <v>32.62941521733669</v>
+      </c>
     </row>
-    <row r="31" spans="1:23">
+    <row r="31" spans="1:29">
       <c r="A31" s="1">
         <v>46068.60839164352</v>
       </c>
@@ -2618,14 +3104,29 @@
       <c r="U31">
         <v>525.8568863994358</v>
       </c>
-      <c r="V31">
-        <v>2.728296036582619</v>
-      </c>
-      <c r="W31" t="b">
+      <c r="V31" t="b">
         <v>1</v>
       </c>
+      <c r="X31">
+        <v>0.250378386</v>
+      </c>
+      <c r="Y31">
+        <v>0.262316154</v>
+      </c>
+      <c r="Z31">
+        <v>0.3626280474884929</v>
+      </c>
+      <c r="AA31">
+        <v>5.968883999999996</v>
+      </c>
+      <c r="AB31">
+        <v>0.06157057675427637</v>
+      </c>
+      <c r="AC31">
+        <v>32.37731178582125</v>
+      </c>
     </row>
-    <row r="32" spans="1:23">
+    <row r="32" spans="1:29">
       <c r="A32" s="1">
         <v>46068.60850796296</v>
       </c>
@@ -2689,14 +3190,29 @@
       <c r="U32">
         <v>528.9693470390806</v>
       </c>
-      <c r="V32">
-        <v>2.133207834186673</v>
-      </c>
-      <c r="W32" t="b">
+      <c r="V32" t="b">
         <v>1</v>
       </c>
+      <c r="X32">
+        <v>0.250365676</v>
+      </c>
+      <c r="Y32">
+        <v>0.262304058</v>
+      </c>
+      <c r="Z32">
+        <v>0.362610521858101</v>
+      </c>
+      <c r="AA32">
+        <v>5.969191000000002</v>
+      </c>
+      <c r="AB32">
+        <v>0.06156459664087068</v>
+      </c>
+      <c r="AC32">
+        <v>32.56578448584574</v>
+      </c>
     </row>
-    <row r="33" spans="1:23">
+    <row r="33" spans="1:29">
       <c r="A33" s="1">
         <v>46068.6086237037</v>
       </c>
@@ -2760,14 +3276,29 @@
       <c r="U33">
         <v>531.0015502768057</v>
       </c>
-      <c r="V33">
-        <v>2.591165363430575</v>
-      </c>
-      <c r="W33" t="b">
+      <c r="V33" t="b">
         <v>1</v>
       </c>
+      <c r="X33">
+        <v>0.25035805</v>
+      </c>
+      <c r="Y33">
+        <v>0.262300238</v>
+      </c>
+      <c r="Z33">
+        <v>0.36260249317215</v>
+      </c>
+      <c r="AA33">
+        <v>5.971093999999994</v>
+      </c>
+      <c r="AB33">
+        <v>0.06154416690375639</v>
+      </c>
+      <c r="AC33">
+        <v>32.68004803638912</v>
+      </c>
     </row>
-    <row r="34" spans="1:23">
+    <row r="34" spans="1:29">
       <c r="A34" s="1">
         <v>46068.60874002315</v>
       </c>
@@ -2831,14 +3362,29 @@
       <c r="U34">
         <v>528.5901494169927</v>
       </c>
-      <c r="V34">
-        <v>1.296694190541836</v>
-      </c>
-      <c r="W34" t="b">
+      <c r="V34" t="b">
         <v>1</v>
       </c>
+      <c r="X34">
+        <v>0.250361546</v>
+      </c>
+      <c r="Y34">
+        <v>0.262291642</v>
+      </c>
+      <c r="Z34">
+        <v>0.3625986888814772</v>
+      </c>
+      <c r="AA34">
+        <v>5.965047999999996</v>
+      </c>
+      <c r="AB34">
+        <v>0.0616042708963682</v>
+      </c>
+      <c r="AC34">
+        <v>32.56341075783617</v>
+      </c>
     </row>
-    <row r="35" spans="1:23">
+    <row r="35" spans="1:29">
       <c r="A35" s="1">
         <v>46068.60885576389</v>
       </c>
@@ -2902,14 +3448,29 @@
       <c r="U35">
         <v>528.260374628371</v>
       </c>
-      <c r="V35">
-        <v>1.496532071906727</v>
-      </c>
-      <c r="W35" t="b">
+      <c r="V35" t="b">
         <v>1</v>
       </c>
+      <c r="X35">
+        <v>0.250353602</v>
+      </c>
+      <c r="Y35">
+        <v>0.262284002</v>
+      </c>
+      <c r="Z35">
+        <v>0.3625876773133782</v>
+      </c>
+      <c r="AA35">
+        <v>5.965200000000003</v>
+      </c>
+      <c r="AB35">
+        <v>0.06160092103026342</v>
+      </c>
+      <c r="AC35">
+        <v>32.54132562089965</v>
+      </c>
     </row>
-    <row r="36" spans="1:23">
+    <row r="36" spans="1:29">
       <c r="A36" s="1">
         <v>46068.60897208333</v>
       </c>
@@ -2973,11 +3534,26 @@
       <c r="U36">
         <v>531.0051358959544</v>
       </c>
-      <c r="V36">
-        <v>1.498589643675443</v>
-      </c>
-      <c r="W36" t="b">
+      <c r="V36" t="b">
         <v>1</v>
+      </c>
+      <c r="X36">
+        <v>0.250339302</v>
+      </c>
+      <c r="Y36">
+        <v>0.262277318</v>
+      </c>
+      <c r="Z36">
+        <v>0.3625729687430109</v>
+      </c>
+      <c r="AA36">
+        <v>5.969007999999995</v>
+      </c>
+      <c r="AB36">
+        <v>0.06156022651629989</v>
+      </c>
+      <c r="AC36">
+        <v>32.68879644707356</v>
       </c>
     </row>
   </sheetData>
